--- a/output/pdf_financials_xlsx/CFW.xlsx
+++ b/output/pdf_financials_xlsx/CFW.xlsx
@@ -8190,46 +8190,46 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>3.644</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>1.905</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>1.799</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>2.475</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>13.214</v>
       </c>
       <c r="J112" s="3" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>10.456</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>7.38</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>7.224</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>1.701</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>3.576</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>22.546</v>
       </c>
       <c r="R112" s="3" t="n">
-        <v>0</v>
+        <v>14.725</v>
       </c>
       <c r="S112" s="1" t="inlineStr">
         <is>
@@ -32278,7 +32278,11 @@
           <t>Proceeds on disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
